--- a/config/auto_configs/2016_Hyundai_Hyundai_Sonata PHEV(LF PHEV)_G 2.0 PHEV.xlsx
+++ b/config/auto_configs/2016_Hyundai_Hyundai_Sonata PHEV(LF PHEV)_G 2.0 PHEV.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="VIN_YMME" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="NWS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="VIN_YMME" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NWS" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -492,7 +492,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:D56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -520,17 +520,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ESC/AHB</t>
+          <t>ECM</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>HMA_002D5</t>
+          <t>HMA_00311</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>C111401</t>
+          <t>U011000</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -542,17 +542,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ESC/AHB</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>HMA_002D5</t>
+          <t>HMA_002BF</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>C123501</t>
+          <t>P0705</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -564,17 +564,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ESC/AHB</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>HMA_002D5</t>
+          <t>HMA_002BF</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>C126801</t>
+          <t>P1615</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -586,17 +586,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ESC/AHB</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HMA_002D5</t>
+          <t>HMA_002BF</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>C126802</t>
+          <t>U0001</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -608,17 +608,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ESC/AHB</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>HMA_002D5</t>
+          <t>HMA_002BF</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>C126808</t>
+          <t>U0100</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -630,17 +630,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>ESC/AHB</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>HMA_002D5</t>
+          <t>HMA_002BF</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>C127502</t>
+          <t>U0110</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -652,17 +652,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ESC/AHB</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>HMA_002D5</t>
+          <t>HMA_002BF</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>C128302</t>
+          <t>U0111</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -674,17 +674,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ESC/AHB</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>HMA_002D5</t>
+          <t>HMA_002BF</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>C128504</t>
+          <t>U0293</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -696,17 +696,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ESC/AHB</t>
+          <t>AT</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>HMA_002D5</t>
+          <t>HMA_002BF</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>C135801</t>
+          <t>U1007</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>C150301</t>
+          <t>C111401</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -750,7 +750,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>C152001</t>
+          <t>C123501</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>C152701</t>
+          <t>C126801</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>C161308</t>
+          <t>C126802</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -816,7 +816,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>C163808</t>
+          <t>C126808</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -838,7 +838,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>C164908</t>
+          <t>C127502</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>C165008</t>
+          <t>C128302</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -882,7 +882,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>C222808</t>
+          <t>C128504</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>C238001</t>
+          <t>C135801</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -916,17 +916,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SRS</t>
+          <t>ESC/AHB</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>HMA_00269</t>
+          <t>HMA_002D5</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>C150301</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -938,20 +938,790 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>ESC/AHB</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>HMA_002D5</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>C152001</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>ESC/AHB</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>HMA_002D5</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>C152701</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>ESC/AHB</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>HMA_002D5</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>C161308</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>ESC/AHB</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>HMA_002D5</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>C163808</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>ESC/AHB</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>HMA_002D5</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>C164908</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>ESC/AHB</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>HMA_002D5</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>C165008</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>ESC/AHB</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>HMA_002D5</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>C222808</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>ESC/AHB</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>HMA_002D5</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>C238001</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
           <t>SRS</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B29" t="inlineStr">
         <is>
           <t>HMA_00268</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>SRS</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>HMA_00269</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>TPMS</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>HMA_0027C</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>A/C</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>HMA_002D3</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>AAF</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>HMA_00313</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>ADM</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>HMA_00271</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>AHLS</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>HMA_0026C</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>AMP</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>HMA_002C2</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>BCM</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>HMA_0029F</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>BMS</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>HMA_002FA</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>BSD-L</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>HMA_002D0</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>BSD-R</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>HMA_002F3</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>CGW</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>HMA_00302</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>CLU</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>HMA_002B0</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>DDM</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>HMA_00270</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>EPB</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>HMA_00274</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>EPS</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>HMA_002FB</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>HCU/LDC</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>HMA_00307</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>LDWS</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>HMA_002C5</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>MCU</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>HMA_00316</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>OBC</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>HMA_0030B</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>ODS</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>HMA_0026A</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>PSM</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>HMA_0026E</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>SCC</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>HMA_00300</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>SJB</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>HMA_0026F</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>SKU</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>HMA_00279</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>TMU</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>HMA_00054</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>00</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>VESS</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>HMA_0030E</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
         <is>
           <t>00</t>
         </is>
